--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -838,7 +838,7 @@
 </t>
   </si>
   <si>
-    <t>Typ av vård- och omsorgsplan (typeOfCarePlan)</t>
+    <t>Typ av vård- och omsorgsplan (typeOfCarePlanEnum)</t>
   </si>
   <si>
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSCarePlan.xlsx
+++ b/StructureDefinition-SEEHDSCarePlan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="526">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1606,6 +1606,10 @@
   </si>
   <si>
     <t>Allows rough dose checking.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP][classCode=SBADM].doseQuantity</t>
@@ -9663,27 +9667,27 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>509</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9709,10 +9713,10 @@
         <v>505</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9763,7 +9767,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9775,27 +9779,27 @@
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>509</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9821,10 +9825,10 @@
         <v>102</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9875,7 +9879,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9893,7 +9897,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -9904,10 +9908,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9933,14 +9937,14 @@
         <v>387</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -9989,7 +9993,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10004,7 +10008,7 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>392</v>
